--- a/data/trans_orig/IP07A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A02-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35757</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49095</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61525</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81267</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>36551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41232</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>54252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73322</t>
+          <t>73951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>48260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64387</t>
+          <t>64006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50513</t>
+          <t>50837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66143</t>
+          <t>65617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>104684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126309</t>
+          <t>125317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>35534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50349</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>27726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67895</t>
+          <t>67064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>87526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27748</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27091</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>58066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75906</t>
+          <t>76316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,27%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61060</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -2435,82 +2435,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6018</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>684</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2637</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>47679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62682</t>
+          <t>62188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83609</t>
+          <t>84185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106405</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50133</t>
+          <t>50312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>27378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42905</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>65350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89078</t>
+          <t>88285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145782</t>
+          <t>145351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>174280</t>
+          <t>175179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>174714</t>
+          <t>172278</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>203520</t>
+          <t>204023</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>328176</t>
+          <t>327218</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>122861</t>
+          <t>122966</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>151491</t>
+          <t>152239</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>120362</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254883</t>
+          <t>250931</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295138</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>64585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44914</t>
+          <t>43806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41837</t>
+          <t>42299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>62610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81992</t>
+          <t>82162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34696</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50477</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37827</t>
+          <t>37057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>53459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77351</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>98936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42347</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>57758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52599</t>
+          <t>52606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>83232</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104934</t>
+          <t>105259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>21633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34417</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>41394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72390</t>
+          <t>72096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26780</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49139</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67135</t>
+          <t>66024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>22015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>37292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>47456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57954</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81064</t>
+          <t>80060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42352</t>
+          <t>41637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59115</t>
+          <t>58027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54088</t>
+          <t>55261</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>86391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109235</t>
+          <t>108084</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108446</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>137516</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165157</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>253635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>294191</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>157650</t>
+          <t>157122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187118</t>
+          <t>185586</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136557</t>
+          <t>133764</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>166568</t>
+          <t>164726</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>298700</t>
+          <t>301737</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>343914</t>
+          <t>342502</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>35252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>49693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41945</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80444</t>
+          <t>81104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101033</t>
+          <t>101089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>30799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>55378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>55311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71297</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>67233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83518</t>
+          <t>83136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127682</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149858</t>
+          <t>149629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28957</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44115</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53275</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>74972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39862</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53035</t>
+          <t>52349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43543</t>
+          <t>44566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57272</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87327</t>
+          <t>87418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105984</t>
+          <t>106777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31377</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38491</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56801</t>
+          <t>56646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55672</t>
+          <t>55134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52801</t>
+          <t>50994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69593</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93676</t>
+          <t>93679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118871</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43097</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>60786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39409</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72338</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>98163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>21660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181633</t>
+          <t>183699</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213641</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>222138</t>
+          <t>219998</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>251939</t>
+          <t>252274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>413795</t>
+          <t>414250</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>458273</t>
+          <t>457316</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118909</t>
+          <t>120662</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>149764</t>
+          <t>149727</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119371</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>215620</t>
+          <t>217282</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259512</t>
+          <t>260519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
